--- a/datos.xlsx
+++ b/datos.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,21 +483,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1121912520</t>
+          <t>1121915682</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Diego Armando</t>
+          <t>Ricardo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Velasquez Torres</t>
+          <t>Tejedor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,50 +506,50 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45090</v>
+        <v>45035</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BOCADILLO VELEÑO GDE 10DP X36UN</t>
+          <t>CHEETOS FRITOLAY X36UN</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>600</v>
+        <v>2500</v>
       </c>
       <c r="K2" t="n">
-        <v>1200</v>
+        <v>5000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>calidad</t>
+          <t>no a realizado el pago</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1121912520</t>
+          <t>1121915682</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Diego Armando</t>
+          <t>Ricardo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Velasquez Torres</t>
+          <t>Tejedor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -558,36 +558,36 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45120</v>
+        <v>45019</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CHEETOS FRITOLAY X36UN</t>
+          <t>CAFÉ AGUILA ROJA 250GR X20UN</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>2500</v>
+        <v>6500</v>
       </c>
       <c r="K3" t="n">
-        <v>10000</v>
+        <v>26000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Prueba de calidad</t>
+          <t>QA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -610,86 +610,398 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45126</v>
+        <v>45090</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ATUN EMILIA ACEITE 175GR X48UN</t>
+          <t>BOCADILLO VELEÑO GDE 10DP X36UN</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="K4" t="n">
-        <v>12000</v>
+        <v>1200</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Prueba de disminución de cantidad de producto</t>
+          <t>calidad</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1121912520</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Diego Armando</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Velasquez Torres</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RADA</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>45120</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CHEETOS FRITOLAY X36UN</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Prueba de calidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1121912520</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Diego Armando</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Velasquez Torres</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RADA</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>45126</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ATUN EMILIA ACEITE 175GR X48UN</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Prueba de disminución de cantidad de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1121915682</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tejedor</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RADA</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>45126</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ATUN EMILIA ACEITE 175GR X48UN</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Prueba de disminución de cantidad de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1121915682</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tejedor</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RADA</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>45126</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>BOCADILLO VELEÑO GDE 10DP X36UN</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>600</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3600</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Prueba de disminución de cantidad de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1121915682</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tejedor</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RADA</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>45126</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ATUN EMILIA ACEITE 175GR X48UN</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>42000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Prueba de disminución de cantidad de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1121915682</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tejedor</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RADA</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>45126</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>BOMB SUPER COCO 24UNX24DS</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>600</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4200</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Prueba de disminución de cantidad de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">Total Suma: </t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>23200</v>
+      <c r="K11" t="n">
+        <v>122000</v>
       </c>
     </row>
   </sheetData>
